--- a/Master/9692r00/9692r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/9692r00/9692r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1214,462 +1214,562 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>6.223</v>
+        <v>3.232</v>
       </c>
       <c r="B39" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C39" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3.399</v>
+        <v>3.3843</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>-0.0712</v>
+        <v>-1.3773</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>0.0367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>5.224</v>
+        <v>6.223</v>
       </c>
       <c r="B40" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D40" s="7" t="n">
-        <v>3.4793</v>
+        <v>3.399</v>
       </c>
       <c r="E40" s="7" t="n">
-        <v>-0.2106</v>
+        <v>-0.0712</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>0.0324</v>
+        <v>0.0367</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>6.123</v>
+        <v>4.237</v>
       </c>
       <c r="B41" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D41" s="7" t="n">
-        <v>3.5221</v>
+        <v>3.424</v>
       </c>
       <c r="E41" s="7" t="n">
-        <v>-0.0794</v>
+        <v>-1.9366</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>0.0058</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>5.124</v>
+        <v>1.234</v>
       </c>
       <c r="B42" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="7" t="n">
-        <v>3.5934</v>
+        <v>3.4249</v>
       </c>
       <c r="E42" s="7" t="n">
-        <v>-0.2272</v>
+        <v>-1.7427</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>0.0057</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>4.225</v>
+        <v>3.238</v>
       </c>
       <c r="B43" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C43" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3.6311</v>
+        <v>3.4268</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.3798</v>
+        <v>-2.1177</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.013</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>4.125</v>
+        <v>5.236</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>3.6642</v>
+        <v>3.4269</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-0.381</v>
+        <v>-1.7637</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0057</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>3.226</v>
+        <v>5.224</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3.7023</v>
+        <v>3.4793</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.5452</v>
+        <v>-0.2106</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0094</v>
+        <v>0.0324</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>2.127</v>
+        <v>6.123</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>3.7165</v>
+        <v>3.5221</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>-0.6123</v>
+        <v>-0.0794</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0011</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>3.126</v>
+        <v>1.228</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>3.7313</v>
+        <v>3.5339</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.5427999999999999</v>
+        <v>-0.9308</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0048</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>1.228</v>
+        <v>5.124</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>3.7613</v>
+        <v>3.5934</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>-0.7876</v>
+        <v>-0.2272</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0002</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>1.128</v>
+        <v>4.225</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C49" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>3.783</v>
+        <v>3.6311</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.7924</v>
+        <v>-0.3798</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0016</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>6.229</v>
+        <v>4.125</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>3.7969</v>
+        <v>3.6642</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-0.7537</v>
+        <v>-0.381</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.013</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>6.129</v>
+        <v>3.226</v>
       </c>
       <c r="B51" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>3.8236</v>
+        <v>3.7023</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0.7539</v>
+        <v>-0.5452</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.0071</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>5.23</v>
+        <v>2.127</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C52" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>3.8339</v>
+        <v>3.7165</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-0.9287</v>
+        <v>-0.6123</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0078</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>5.13</v>
+        <v>3.126</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>3.8557</v>
+        <v>3.7313</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-0.9333</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.0064</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>4.231</v>
+        <v>1.128</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>3.8886</v>
+        <v>3.783</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>-1.182</v>
+        <v>-0.7924</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0001</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>4.131</v>
+        <v>6.229</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>3.899</v>
+        <v>3.7969</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-1.1681</v>
+        <v>-0.7537</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0026</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>3.132</v>
+        <v>6.129</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>3.9057</v>
+        <v>3.8236</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>-1.3455</v>
+        <v>-0.7539</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.0007</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>5.136</v>
+        <v>5.23</v>
       </c>
       <c r="B57" s="6" t="n">
         <v>5</v>
       </c>
       <c r="C57" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>3.9214</v>
+        <v>3.8339</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-1.6842</v>
+        <v>-0.9287</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0008</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>6.135</v>
+        <v>5.13</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>3.9216</v>
+        <v>3.8557</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>-1.5559</v>
+        <v>-0.9333</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0.0029</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>1.134</v>
+        <v>4.231</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C59" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>3.9236</v>
+        <v>3.8886</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-1.6415</v>
+        <v>-1.182</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.0019</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
+        <v>4.131</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>3.899</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>-1.1681</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.0026</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>3.132</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>3.9057</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>-1.3455</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>5.136</v>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>3.9214</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>-1.6842</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0.0008</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>6.135</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>3.9216</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>-1.5559</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>0.0029</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>3.9236</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>-1.6415</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0.0019</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
         <v>2.133</v>
       </c>
-      <c r="B60" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="7" t="n">
+      <c r="B65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="n">
         <v>3.924</v>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E65" s="7" t="n">
         <v>-1.484</v>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F65" s="7" t="n">
         <v>0.0017</v>
       </c>
     </row>
-    <row r="62">
-      <c r="E62" s="8" t="inlineStr">
+    <row r="67">
+      <c r="E67" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F62" s="9" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="E63" s="8" t="inlineStr">
+      <c r="F67" s="9" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="E68" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F63" s="10" t="n">
-        <v>0.9426</v>
+      <c r="F68" s="10" t="n">
+        <v>0.9437</v>
       </c>
     </row>
   </sheetData>
